--- a/docs/modelos_importacao/04_Exemplo_Historico_Sinistros_36_Meses_TESTE.xlsx
+++ b/docs/modelos_importacao/04_Exemplo_Historico_Sinistros_36_Meses_TESTE.xlsx
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Leia-me" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Sinistros'!$A$1:$G$37</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Sinistros'!$A$1:$G$178</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Leia-me'!$A$1:$B$7</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -20,8 +20,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="165" formatCode="yyyy-mm-dd h:mm:ss"/>
   </numFmts>
   <fonts count="2">
     <font>
@@ -435,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G37"/>
+  <dimension ref="A1:G178"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -486,19 +487,19 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
-        <v>44932</v>
+        <v>44940</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>HOSPITALIZATION</t>
+          <t>EMERGENCY</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>122918.07</v>
+        <v>75919.27</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>DEMO-PESS-001</t>
+          <t>DEMO-PESS-018</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -517,19 +518,19 @@
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
-        <v>44964</v>
+        <v>44955</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>OUTPATIENT</t>
+          <t>AMBULATORY_SURGERY</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>24207.98</v>
+        <v>160191.22</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>DEMO-PESS-002</t>
+          <t>DEMO-PESS-020</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -548,19 +549,19 @@
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
-        <v>44993</v>
+        <v>44957</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>EMERGENCY</t>
+          <t>PHARMACY</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>54249.86</v>
+        <v>17260.1</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>DEMO-PESS-003</t>
+          <t>DEMO-PESS-028</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -579,15 +580,15 @@
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
-        <v>45025</v>
+        <v>44961</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>PHARMACY</t>
+          <t>EMERGENCY</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>12773.84</v>
+        <v>43670.61</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -610,7 +611,7 @@
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
-        <v>45056</v>
+        <v>44964</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
@@ -618,11 +619,11 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>75526.42</v>
+        <v>348608.7</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>DEMO-PESS-001</t>
+          <t>DEMO-PESS-012</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -641,19 +642,19 @@
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
-        <v>45088</v>
+        <v>44969</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>OUTPATIENT</t>
+          <t>VACCINATION</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>21040.22</v>
+        <v>13051.36</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>DEMO-PESS-002</t>
+          <t>DEMO-PESS-026</t>
         </is>
       </c>
       <c r="E7" t="n">
@@ -672,19 +673,19 @@
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
-        <v>45119</v>
+        <v>44976</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>EMERGENCY</t>
+          <t>ENDEMIC_DISEASES</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>53898.98</v>
+        <v>28232.85</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>DEMO-PESS-003</t>
+          <t>DEMO-PESS-001</t>
         </is>
       </c>
       <c r="E8" t="n">
@@ -703,19 +704,19 @@
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
-        <v>45151</v>
+        <v>44981</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>PHARMACY</t>
+          <t>EMERGENCY</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>12690.93</v>
+        <v>47125.65</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>DEMO-PESS-004</t>
+          <t>DEMO-PESS-018</t>
         </is>
       </c>
       <c r="E9" t="n">
@@ -734,19 +735,19 @@
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
-        <v>45183</v>
+        <v>44984</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>HOSPITALIZATION</t>
+          <t>PHARMACY</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>116450.56</v>
+        <v>25601.2</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>DEMO-PESS-001</t>
+          <t>DEMO-PESS-016</t>
         </is>
       </c>
       <c r="E10" t="n">
@@ -765,7 +766,7 @@
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
-        <v>45214</v>
+        <v>44990</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
@@ -773,11 +774,11 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>19486.19</v>
+        <v>40923.67</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>DEMO-PESS-002</t>
+          <t>DEMO-PESS-023</t>
         </is>
       </c>
       <c r="E11" t="n">
@@ -796,23 +797,23 @@
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
-        <v>45246</v>
+        <v>44995</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>EMERGENCY</t>
+          <t>ENDEMIC_DISEASES</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>30797.56</v>
+        <v>15742.18</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>DEMO-PESS-003</t>
+          <t>DEMO-PESS-023</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>2858.01</v>
+        <v>0</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -827,7 +828,7 @@
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
-        <v>45277</v>
+        <v>45000</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
@@ -835,15 +836,15 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>17443.72</v>
+        <v>15288.78</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>DEMO-PESS-004</t>
+          <t>DEMO-PESS-013</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1132.64</v>
+        <v>0</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -858,19 +859,19 @@
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
-        <v>45297</v>
+        <v>45003</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>OUTPATIENT</t>
+          <t>PHYSIOTHERAPY</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>34391.72</v>
+        <v>39938.2</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>DEMO-PESS-002</t>
+          <t>DEMO-PESS-004</t>
         </is>
       </c>
       <c r="E14" t="n">
@@ -889,19 +890,19 @@
     </row>
     <row r="15">
       <c r="A15" s="2" t="n">
-        <v>45329</v>
+        <v>45011</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>EMERGENCY</t>
+          <t>PHARMACY</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>38573.26</v>
+        <v>22503.23</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>DEMO-PESS-003</t>
+          <t>DEMO-PESS-020</t>
         </is>
       </c>
       <c r="E15" t="n">
@@ -920,19 +921,19 @@
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
-        <v>45359</v>
+        <v>45024</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>PHARMACY</t>
+          <t>OUTPATIENT</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>17768.37</v>
+        <v>37272.27</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>DEMO-PESS-004</t>
+          <t>DEMO-PESS-027</t>
         </is>
       </c>
       <c r="E16" t="n">
@@ -951,19 +952,19 @@
     </row>
     <row r="17">
       <c r="A17" s="2" t="n">
-        <v>45391</v>
+        <v>45024</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>HOSPITALIZATION</t>
+          <t>PHARMACY</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>128025.21</v>
+        <v>24691.83</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>DEMO-PESS-001</t>
+          <t>DEMO-PESS-004</t>
         </is>
       </c>
       <c r="E17" t="n">
@@ -982,19 +983,19 @@
     </row>
     <row r="18">
       <c r="A18" s="2" t="n">
-        <v>45422</v>
+        <v>45032</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>OUTPATIENT</t>
+          <t>EMERGENCY</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>21166.14</v>
+        <v>58341.71</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>DEMO-PESS-002</t>
+          <t>DEMO-PESS-026</t>
         </is>
       </c>
       <c r="E18" t="n">
@@ -1013,19 +1014,19 @@
     </row>
     <row r="19">
       <c r="A19" s="2" t="n">
-        <v>45454</v>
+        <v>45033</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>EMERGENCY</t>
+          <t>PHARMACY</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>38028.53</v>
+        <v>11690.16</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>DEMO-PESS-003</t>
+          <t>DEMO-PESS-014</t>
         </is>
       </c>
       <c r="E19" t="n">
@@ -1044,19 +1045,19 @@
     </row>
     <row r="20">
       <c r="A20" s="2" t="n">
-        <v>45485</v>
+        <v>45036</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>PHARMACY</t>
+          <t>OUTPATIENT</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>14208.51</v>
+        <v>26170.51</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>DEMO-PESS-004</t>
+          <t>DEMO-PESS-005</t>
         </is>
       </c>
       <c r="E20" t="n">
@@ -1075,19 +1076,19 @@
     </row>
     <row r="21">
       <c r="A21" s="2" t="n">
-        <v>45517</v>
+        <v>45039</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>HOSPITALIZATION</t>
+          <t>OUTPATIENT</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>120224.41</v>
+        <v>29266.15</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>DEMO-PESS-001</t>
+          <t>DEMO-PESS-022</t>
         </is>
       </c>
       <c r="E21" t="n">
@@ -1106,19 +1107,19 @@
     </row>
     <row r="22">
       <c r="A22" s="2" t="n">
-        <v>45549</v>
+        <v>45047</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>OUTPATIENT</t>
+          <t>DENTAL</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>32990.56</v>
+        <v>16821.01</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>DEMO-PESS-002</t>
+          <t>DEMO-PESS-021</t>
         </is>
       </c>
       <c r="E22" t="n">
@@ -1137,19 +1138,19 @@
     </row>
     <row r="23">
       <c r="A23" s="2" t="n">
-        <v>45580</v>
+        <v>45059</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>EMERGENCY</t>
+          <t>OUTPATIENT</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>46435.94</v>
+        <v>34101.88</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>DEMO-PESS-003</t>
+          <t>DEMO-PESS-010</t>
         </is>
       </c>
       <c r="E23" t="n">
@@ -1168,23 +1169,23 @@
     </row>
     <row r="24">
       <c r="A24" s="2" t="n">
-        <v>45612</v>
+        <v>45059</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>PHARMACY</t>
+          <t>DENTAL</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>23492.08</v>
+        <v>38818.68</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>DEMO-PESS-004</t>
+          <t>DEMO-PESS-010</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>567.3099999999999</v>
+        <v>0</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -1199,23 +1200,23 @@
     </row>
     <row r="25">
       <c r="A25" s="2" t="n">
-        <v>45643</v>
+        <v>45067</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>HOSPITALIZATION</t>
+          <t>PHARMACY</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>90396.46000000001</v>
+        <v>17041.79</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>DEMO-PESS-001</t>
+          <t>DEMO-PESS-016</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>3275.14</v>
+        <v>0</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -1230,19 +1231,19 @@
     </row>
     <row r="26">
       <c r="A26" s="2" t="n">
-        <v>45663</v>
+        <v>45069</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>EMERGENCY</t>
+          <t>HOSPITALIZATION</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>45614.81</v>
+        <v>614732.35</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>DEMO-PESS-003</t>
+          <t>DEMO-PESS-018</t>
         </is>
       </c>
       <c r="E26" t="n">
@@ -1261,19 +1262,19 @@
     </row>
     <row r="27">
       <c r="A27" s="2" t="n">
-        <v>45695</v>
+        <v>45077</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>PHARMACY</t>
+          <t>PHYSIOTHERAPY</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>13660.48</v>
+        <v>38329.1</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>DEMO-PESS-004</t>
+          <t>DEMO-PESS-017</t>
         </is>
       </c>
       <c r="E27" t="n">
@@ -1292,19 +1293,19 @@
     </row>
     <row r="28">
       <c r="A28" s="2" t="n">
-        <v>45724</v>
+        <v>45084</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>HOSPITALIZATION</t>
+          <t>PHARMACY</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>97914.31</v>
+        <v>11722.43</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>DEMO-PESS-001</t>
+          <t>DEMO-PESS-016</t>
         </is>
       </c>
       <c r="E28" t="n">
@@ -1323,7 +1324,7 @@
     </row>
     <row r="29">
       <c r="A29" s="2" t="n">
-        <v>45756</v>
+        <v>45092</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
@@ -1331,11 +1332,11 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>24876.44</v>
+        <v>42254.79</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>DEMO-PESS-002</t>
+          <t>DEMO-PESS-004</t>
         </is>
       </c>
       <c r="E29" t="n">
@@ -1354,19 +1355,19 @@
     </row>
     <row r="30">
       <c r="A30" s="2" t="n">
-        <v>45787</v>
+        <v>45099</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>EMERGENCY</t>
+          <t>PHARMACY</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>37013.19</v>
+        <v>25959.86</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>DEMO-PESS-003</t>
+          <t>DEMO-PESS-027</t>
         </is>
       </c>
       <c r="E30" t="n">
@@ -1385,7 +1386,7 @@
     </row>
     <row r="31">
       <c r="A31" s="2" t="n">
-        <v>45819</v>
+        <v>45100</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
@@ -1393,11 +1394,11 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>13713.89</v>
+        <v>23271.85</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>DEMO-PESS-004</t>
+          <t>DEMO-PESS-017</t>
         </is>
       </c>
       <c r="E31" t="n">
@@ -1416,19 +1417,19 @@
     </row>
     <row r="32">
       <c r="A32" s="2" t="n">
-        <v>45850</v>
+        <v>45102</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>HOSPITALIZATION</t>
+          <t>PHARMACY</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>104842.03</v>
+        <v>24175.82</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>DEMO-PESS-001</t>
+          <t>DEMO-PESS-026</t>
         </is>
       </c>
       <c r="E32" t="n">
@@ -1447,7 +1448,7 @@
     </row>
     <row r="33">
       <c r="A33" s="2" t="n">
-        <v>45882</v>
+        <v>45107</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
@@ -1455,11 +1456,11 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>20306.89</v>
+        <v>43853.85</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>DEMO-PESS-002</t>
+          <t>DEMO-PESS-014</t>
         </is>
       </c>
       <c r="E33" t="n">
@@ -1478,19 +1479,19 @@
     </row>
     <row r="34">
       <c r="A34" s="2" t="n">
-        <v>45914</v>
+        <v>45114</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>EMERGENCY</t>
+          <t>PHARMACY</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>39734.79</v>
+        <v>22446.13</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>DEMO-PESS-003</t>
+          <t>DEMO-PESS-014</t>
         </is>
       </c>
       <c r="E34" t="n">
@@ -1503,25 +1504,25 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>PAGO</t>
+          <t>REJEITADO</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="n">
-        <v>45945</v>
+        <v>45114</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>PHARMACY</t>
+          <t>EMERGENCY</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>13173.96</v>
+        <v>41109.44</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>DEMO-PESS-004</t>
+          <t>DEMO-PESS-020</t>
         </is>
       </c>
       <c r="E35" t="n">
@@ -1540,23 +1541,23 @@
     </row>
     <row r="36">
       <c r="A36" s="2" t="n">
-        <v>45977</v>
+        <v>45125</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>HOSPITALIZATION</t>
+          <t>PHARMACY</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>73530.67</v>
+        <v>26507.92</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>DEMO-PESS-001</t>
+          <t>DEMO-PESS-003</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>3301.25</v>
+        <v>0</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -1571,7 +1572,7 @@
     </row>
     <row r="37">
       <c r="A37" s="2" t="n">
-        <v>46008</v>
+        <v>45125</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
@@ -1579,29 +1580,4400 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>33956.06</v>
+        <v>43560.11</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
+          <t>DEMO-PESS-022</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>0</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>AOA</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>PAGO</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="n">
+        <v>45128</v>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>AMBULATORY_SURGERY</t>
+        </is>
+      </c>
+      <c r="C38" t="n">
+        <v>167963.91</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>DEMO-PESS-016</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>0</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>AOA</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>PAGO</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="n">
+        <v>45137</v>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>OUTPATIENT</t>
+        </is>
+      </c>
+      <c r="C39" t="n">
+        <v>12463.07</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>DEMO-PESS-001</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>0</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>AOA</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>PAGO</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="n">
+        <v>45141</v>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>PHARMACY</t>
+        </is>
+      </c>
+      <c r="C40" t="n">
+        <v>15191.14</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>DEMO-PESS-006</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>0</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>AOA</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>PAGO</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="n">
+        <v>45143</v>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>ENDEMIC_DISEASES</t>
+        </is>
+      </c>
+      <c r="C41" t="n">
+        <v>31374.11</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>DEMO-PESS-016</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>0</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>AOA</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>PAGO</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="n">
+        <v>45149</v>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>OUTPATIENT</t>
+        </is>
+      </c>
+      <c r="C42" t="n">
+        <v>33931.18</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>DEMO-PESS-019</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>0</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>AOA</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>PAGO</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="n">
+        <v>45169</v>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>ENDEMIC_DISEASES</t>
+        </is>
+      </c>
+      <c r="C43" t="n">
+        <v>40821.01</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>DEMO-PESS-023</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>0</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>AOA</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>PAGO</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="n">
+        <v>45169</v>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>EMERGENCY</t>
+        </is>
+      </c>
+      <c r="C44" t="n">
+        <v>63878.87</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>DEMO-PESS-023</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>0</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>AOA</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>PAGO</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="n">
+        <v>45170</v>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>OUTPATIENT</t>
+        </is>
+      </c>
+      <c r="C45" t="n">
+        <v>43641.21</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>DEMO-PESS-013</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>0</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>AOA</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>PAGO</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="n">
+        <v>45171</v>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>PHYSIOTHERAPY</t>
+        </is>
+      </c>
+      <c r="C46" t="n">
+        <v>53351.99</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>DEMO-PESS-021</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>0</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>AOA</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>PAGO</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="n">
+        <v>45195</v>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>PHARMACY</t>
+        </is>
+      </c>
+      <c r="C47" t="n">
+        <v>9267.799999999999</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>DEMO-PESS-026</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>0</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>AOA</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>PAGO</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="n">
+        <v>45199</v>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>DENTAL</t>
+        </is>
+      </c>
+      <c r="C48" t="n">
+        <v>47231.61</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>DEMO-PESS-017</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>0</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>AOA</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>PAGO</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="n">
+        <v>45205</v>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>EMERGENCY</t>
+        </is>
+      </c>
+      <c r="C49" t="n">
+        <v>35002.89</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>DEMO-PESS-017</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>0</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>AOA</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>PAGO</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="n">
+        <v>45215</v>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>CHECKUP_PREVENTIVE</t>
+        </is>
+      </c>
+      <c r="C50" t="n">
+        <v>34129.3</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>DEMO-PESS-019</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>0</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>AOA</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>PAGO</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="n">
+        <v>45219</v>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>OUTPATIENT</t>
+        </is>
+      </c>
+      <c r="C51" t="n">
+        <v>23101.82</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>DEMO-PESS-020</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>0</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>AOA</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>PAGO</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="n">
+        <v>45221</v>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>PHARMACY</t>
+        </is>
+      </c>
+      <c r="C52" t="n">
+        <v>12680.78</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>DEMO-PESS-011</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>0</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>AOA</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>PAGO</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="n">
+        <v>45230</v>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>CHECKUP_PREVENTIVE</t>
+        </is>
+      </c>
+      <c r="C53" t="n">
+        <v>18438.43</v>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>DEMO-PESS-017</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>0</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>AOA</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>PAGO</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="n">
+        <v>45233</v>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>HOSPITALIZATION</t>
+        </is>
+      </c>
+      <c r="C54" t="n">
+        <v>423676.98</v>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
           <t>DEMO-PESS-002</t>
         </is>
       </c>
-      <c r="E37" t="n">
-        <v>788.41</v>
-      </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>AOA</t>
-        </is>
-      </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>PAGO</t>
+      <c r="E54" t="n">
+        <v>0</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>AOA</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>PAGO</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="n">
+        <v>45237</v>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>ENDEMIC_DISEASES</t>
+        </is>
+      </c>
+      <c r="C55" t="n">
+        <v>29515.22</v>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>DEMO-PESS-022</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>0</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>AOA</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>REJEITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="n">
+        <v>45257</v>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>PHARMACY</t>
+        </is>
+      </c>
+      <c r="C56" t="n">
+        <v>7060.12</v>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>DEMO-PESS-028</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>0</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>AOA</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>PAGO</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="n">
+        <v>45260</v>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>OUTPATIENT</t>
+        </is>
+      </c>
+      <c r="C57" t="n">
+        <v>17721.01</v>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>DEMO-PESS-021</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>0</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>AOA</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>PAGO</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="n">
+        <v>45273</v>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>OPTICAL</t>
+        </is>
+      </c>
+      <c r="C58" t="n">
+        <v>34548.24</v>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>DEMO-PESS-018</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>0</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>AOA</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>PAGO</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="n">
+        <v>45277</v>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>OUTPATIENT</t>
+        </is>
+      </c>
+      <c r="C59" t="n">
+        <v>19217.88</v>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>DEMO-PESS-029</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>0</v>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>AOA</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>PAGO</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="n">
+        <v>45291</v>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>PHARMACY</t>
+        </is>
+      </c>
+      <c r="C60" t="n">
+        <v>9029.879999999999</v>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>DEMO-PESS-022</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>0</v>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>AOA</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>PAGO</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="n">
+        <v>45292</v>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>OUTPATIENT</t>
+        </is>
+      </c>
+      <c r="C61" t="n">
+        <v>43471.24</v>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>DEMO-PESS-029</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>0</v>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>AOA</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>PAGO</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="n">
+        <v>45300</v>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>PHARMACY</t>
+        </is>
+      </c>
+      <c r="C62" t="n">
+        <v>23955.35</v>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>DEMO-PESS-028</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>0</v>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>AOA</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>PAGO</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="n">
+        <v>45301</v>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>DENTAL</t>
+        </is>
+      </c>
+      <c r="C63" t="n">
+        <v>40723.52</v>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>DEMO-PESS-011</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>0</v>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>AOA</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>PAGO</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="n">
+        <v>45304</v>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>OPTICAL</t>
+        </is>
+      </c>
+      <c r="C64" t="n">
+        <v>35671.82</v>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>DEMO-PESS-012</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>0</v>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>AOA</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>PAGO</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="n">
+        <v>45306</v>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>OUTPATIENT</t>
+        </is>
+      </c>
+      <c r="C65" t="n">
+        <v>28420.88</v>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>DEMO-PESS-025</t>
+        </is>
+      </c>
+      <c r="E65" t="n">
+        <v>0</v>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>AOA</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>PAGO</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="n">
+        <v>45306</v>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>PHARMACY</t>
+        </is>
+      </c>
+      <c r="C66" t="n">
+        <v>8642.32</v>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>DEMO-PESS-026</t>
+        </is>
+      </c>
+      <c r="E66" t="n">
+        <v>0</v>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>AOA</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>PAGO</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="n">
+        <v>45328</v>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>PHARMACY</t>
+        </is>
+      </c>
+      <c r="C67" t="n">
+        <v>13737.44</v>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>DEMO-PESS-022</t>
+        </is>
+      </c>
+      <c r="E67" t="n">
+        <v>0</v>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>AOA</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>PAGO</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="n">
+        <v>45332</v>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>OUTPATIENT</t>
+        </is>
+      </c>
+      <c r="C68" t="n">
+        <v>30573.44</v>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>DEMO-PESS-022</t>
+        </is>
+      </c>
+      <c r="E68" t="n">
+        <v>0</v>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>AOA</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>PAGO</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="n">
+        <v>45336</v>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>EMERGENCY</t>
+        </is>
+      </c>
+      <c r="C69" t="n">
+        <v>60428.91</v>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>DEMO-PESS-027</t>
+        </is>
+      </c>
+      <c r="E69" t="n">
+        <v>0</v>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>AOA</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>PAGO</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="n">
+        <v>45340</v>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>EMERGENCY</t>
+        </is>
+      </c>
+      <c r="C70" t="n">
+        <v>39075.26</v>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>DEMO-PESS-020</t>
+        </is>
+      </c>
+      <c r="E70" t="n">
+        <v>0</v>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>AOA</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>PAGO</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="n">
+        <v>45340</v>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>ENDEMIC_DISEASES</t>
+        </is>
+      </c>
+      <c r="C71" t="n">
+        <v>37537.39</v>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>DEMO-PESS-024</t>
+        </is>
+      </c>
+      <c r="E71" t="n">
+        <v>0</v>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>AOA</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>PAGO</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="n">
+        <v>45344</v>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>OPTICAL</t>
+        </is>
+      </c>
+      <c r="C72" t="n">
+        <v>31385.8</v>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>DEMO-PESS-001</t>
+        </is>
+      </c>
+      <c r="E72" t="n">
+        <v>0</v>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>AOA</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>PAGO</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="n">
+        <v>45357</v>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>ENDEMIC_DISEASES</t>
+        </is>
+      </c>
+      <c r="C73" t="n">
+        <v>34378.33</v>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>DEMO-PESS-004</t>
+        </is>
+      </c>
+      <c r="E73" t="n">
+        <v>0</v>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>AOA</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>PAGO</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="n">
+        <v>45360</v>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>OUTPATIENT</t>
+        </is>
+      </c>
+      <c r="C74" t="n">
+        <v>15182.21</v>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>DEMO-PESS-014</t>
+        </is>
+      </c>
+      <c r="E74" t="n">
+        <v>0</v>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>AOA</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>PAGO</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="n">
+        <v>45360</v>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>PHARMACY</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>18938.39</v>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>DEMO-PESS-003</t>
+        </is>
+      </c>
+      <c r="E75" t="n">
+        <v>0</v>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>AOA</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>PAGO</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="n">
+        <v>45373</v>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>OUTPATIENT</t>
+        </is>
+      </c>
+      <c r="C76" t="n">
+        <v>13994.06</v>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>DEMO-PESS-012</t>
+        </is>
+      </c>
+      <c r="E76" t="n">
+        <v>0</v>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>AOA</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>PAGO</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="2" t="n">
+        <v>45383</v>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>OUTPATIENT</t>
+        </is>
+      </c>
+      <c r="C77" t="n">
+        <v>13891.28</v>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>DEMO-PESS-008</t>
+        </is>
+      </c>
+      <c r="E77" t="n">
+        <v>0</v>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>AOA</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>PAGO</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="n">
+        <v>45386</v>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>OUTPATIENT</t>
+        </is>
+      </c>
+      <c r="C78" t="n">
+        <v>15097.71</v>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>DEMO-PESS-018</t>
+        </is>
+      </c>
+      <c r="E78" t="n">
+        <v>0</v>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>AOA</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>PAGO</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="n">
+        <v>45388</v>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>CHECKUP_PREVENTIVE</t>
+        </is>
+      </c>
+      <c r="C79" t="n">
+        <v>22434.59</v>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>DEMO-PESS-003</t>
+        </is>
+      </c>
+      <c r="E79" t="n">
+        <v>0</v>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>AOA</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>PAGO</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="n">
+        <v>45410</v>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>OUTPATIENT</t>
+        </is>
+      </c>
+      <c r="C80" t="n">
+        <v>41635.78</v>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>DEMO-PESS-025</t>
+        </is>
+      </c>
+      <c r="E80" t="n">
+        <v>0</v>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>AOA</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>PAGO</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="n">
+        <v>45412</v>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>EMERGENCY</t>
+        </is>
+      </c>
+      <c r="C81" t="n">
+        <v>80733.64999999999</v>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>DEMO-PESS-011</t>
+        </is>
+      </c>
+      <c r="E81" t="n">
+        <v>0</v>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>AOA</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>PAGO</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="n">
+        <v>45422</v>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>OUTPATIENT</t>
+        </is>
+      </c>
+      <c r="C82" t="n">
+        <v>43253.1</v>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>DEMO-PESS-012</t>
+        </is>
+      </c>
+      <c r="E82" t="n">
+        <v>0</v>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>AOA</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>PAGO</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="2" t="n">
+        <v>45423</v>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>CHECKUP_PREVENTIVE</t>
+        </is>
+      </c>
+      <c r="C83" t="n">
+        <v>28332.36</v>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>DEMO-PESS-020</t>
+        </is>
+      </c>
+      <c r="E83" t="n">
+        <v>0</v>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>AOA</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>PAGO</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="n">
+        <v>45429</v>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>PHARMACY</t>
+        </is>
+      </c>
+      <c r="C84" t="n">
+        <v>20990.88</v>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>DEMO-PESS-030</t>
+        </is>
+      </c>
+      <c r="E84" t="n">
+        <v>0</v>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>AOA</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>PAGO</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="n">
+        <v>45433</v>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>EMERGENCY</t>
+        </is>
+      </c>
+      <c r="C85" t="n">
+        <v>71424.06</v>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>DEMO-PESS-002</t>
+        </is>
+      </c>
+      <c r="E85" t="n">
+        <v>0</v>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>AOA</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>PAGO</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="n">
+        <v>45434</v>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>PHARMACY</t>
+        </is>
+      </c>
+      <c r="C86" t="n">
+        <v>25324.87</v>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>DEMO-PESS-022</t>
+        </is>
+      </c>
+      <c r="E86" t="n">
+        <v>0</v>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>AOA</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>PAGO</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="2" t="n">
+        <v>45435</v>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>OUTPATIENT</t>
+        </is>
+      </c>
+      <c r="C87" t="n">
+        <v>26412.46</v>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>DEMO-PESS-001</t>
+        </is>
+      </c>
+      <c r="E87" t="n">
+        <v>0</v>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>AOA</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>PAGO</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="n">
+        <v>45445</v>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>OUTPATIENT</t>
+        </is>
+      </c>
+      <c r="C88" t="n">
+        <v>35815.38</v>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>DEMO-PESS-004</t>
+        </is>
+      </c>
+      <c r="E88" t="n">
+        <v>0</v>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>AOA</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>PAGO</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="2" t="n">
+        <v>45447</v>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>DENTAL</t>
+        </is>
+      </c>
+      <c r="C89" t="n">
+        <v>31331.81</v>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>DEMO-PESS-014</t>
+        </is>
+      </c>
+      <c r="E89" t="n">
+        <v>0</v>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>AOA</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>PAGO</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="2" t="n">
+        <v>45447</v>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>MEDICAL_EVACUATION</t>
+        </is>
+      </c>
+      <c r="C90" t="n">
+        <v>9500</v>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>DEMO-PESS-002</t>
+        </is>
+      </c>
+      <c r="E90" t="n">
+        <v>0</v>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>PAGO</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="2" t="n">
+        <v>45453</v>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>HOSPITALIZATION</t>
+        </is>
+      </c>
+      <c r="C91" t="n">
+        <v>513563.32</v>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>DEMO-PESS-025</t>
+        </is>
+      </c>
+      <c r="E91" t="n">
+        <v>0</v>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>AOA</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>PAGO</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="2" t="n">
+        <v>45472</v>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>PHARMACY</t>
+        </is>
+      </c>
+      <c r="C92" t="n">
+        <v>6445.94</v>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>DEMO-PESS-011</t>
+        </is>
+      </c>
+      <c r="E92" t="n">
+        <v>0</v>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>AOA</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>PAGO</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="2" t="n">
+        <v>45485</v>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>EMERGENCY</t>
+        </is>
+      </c>
+      <c r="C93" t="n">
+        <v>51994.38</v>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>DEMO-PESS-013</t>
+        </is>
+      </c>
+      <c r="E93" t="n">
+        <v>0</v>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>AOA</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>PAGO</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="2" t="n">
+        <v>45487</v>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>OUTPATIENT</t>
+        </is>
+      </c>
+      <c r="C94" t="n">
+        <v>33865.57</v>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>DEMO-PESS-025</t>
+        </is>
+      </c>
+      <c r="E94" t="n">
+        <v>0</v>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>AOA</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>PAGO</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="2" t="n">
+        <v>45491</v>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>OUTPATIENT</t>
+        </is>
+      </c>
+      <c r="C95" t="n">
+        <v>12937.77</v>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>DEMO-PESS-023</t>
+        </is>
+      </c>
+      <c r="E95" t="n">
+        <v>0</v>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>AOA</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>PAGO</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="2" t="n">
+        <v>45494</v>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>EMERGENCY</t>
+        </is>
+      </c>
+      <c r="C96" t="n">
+        <v>44645.68</v>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>DEMO-PESS-014</t>
+        </is>
+      </c>
+      <c r="E96" t="n">
+        <v>0</v>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>AOA</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>PAGO</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="2" t="n">
+        <v>45495</v>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>CHECKUP_PREVENTIVE</t>
+        </is>
+      </c>
+      <c r="C97" t="n">
+        <v>27433.27</v>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>DEMO-PESS-029</t>
+        </is>
+      </c>
+      <c r="E97" t="n">
+        <v>0</v>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>AOA</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>PAGO</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="2" t="n">
+        <v>45506</v>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>OUTPATIENT</t>
+        </is>
+      </c>
+      <c r="C98" t="n">
+        <v>33457.04</v>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>DEMO-PESS-027</t>
+        </is>
+      </c>
+      <c r="E98" t="n">
+        <v>0</v>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>AOA</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>PAGO</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="2" t="n">
+        <v>45512</v>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>DENTAL</t>
+        </is>
+      </c>
+      <c r="C99" t="n">
+        <v>16284.91</v>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>DEMO-PESS-009</t>
+        </is>
+      </c>
+      <c r="E99" t="n">
+        <v>0</v>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>AOA</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>PAGO</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="2" t="n">
+        <v>45513</v>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>PHARMACY</t>
+        </is>
+      </c>
+      <c r="C100" t="n">
+        <v>13495.69</v>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>DEMO-PESS-017</t>
+        </is>
+      </c>
+      <c r="E100" t="n">
+        <v>0</v>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>AOA</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>PAGO</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="2" t="n">
+        <v>45518</v>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>PHARMACY</t>
+        </is>
+      </c>
+      <c r="C101" t="n">
+        <v>11803.95</v>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>DEMO-PESS-011</t>
+        </is>
+      </c>
+      <c r="E101" t="n">
+        <v>0</v>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>AOA</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>PAGO</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="2" t="n">
+        <v>45525</v>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>OUTPATIENT</t>
+        </is>
+      </c>
+      <c r="C102" t="n">
+        <v>31590.47</v>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>DEMO-PESS-027</t>
+        </is>
+      </c>
+      <c r="E102" t="n">
+        <v>0</v>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>AOA</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>PAGO</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="2" t="n">
+        <v>45543</v>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>PHARMACY</t>
+        </is>
+      </c>
+      <c r="C103" t="n">
+        <v>20941.15</v>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>DEMO-PESS-028</t>
+        </is>
+      </c>
+      <c r="E103" t="n">
+        <v>0</v>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>AOA</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>PAGO</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="2" t="n">
+        <v>45544</v>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>EMERGENCY</t>
+        </is>
+      </c>
+      <c r="C104" t="n">
+        <v>47339.72</v>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>DEMO-PESS-007</t>
+        </is>
+      </c>
+      <c r="E104" t="n">
+        <v>0</v>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>AOA</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>PAGO</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="2" t="n">
+        <v>45547</v>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>ENDEMIC_DISEASES</t>
+        </is>
+      </c>
+      <c r="C105" t="n">
+        <v>43530</v>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>DEMO-PESS-008</t>
+        </is>
+      </c>
+      <c r="E105" t="n">
+        <v>0</v>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>AOA</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>PAGO</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="2" t="n">
+        <v>45559</v>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>OUTPATIENT</t>
+        </is>
+      </c>
+      <c r="C106" t="n">
+        <v>41899.49</v>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>DEMO-PESS-013</t>
+        </is>
+      </c>
+      <c r="E106" t="n">
+        <v>0</v>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>AOA</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>PAGO</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="2" t="n">
+        <v>45562</v>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>OUTPATIENT</t>
+        </is>
+      </c>
+      <c r="C107" t="n">
+        <v>12376.51</v>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>DEMO-PESS-008</t>
+        </is>
+      </c>
+      <c r="E107" t="n">
+        <v>0</v>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>AOA</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>PAGO</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="2" t="n">
+        <v>45579</v>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>PHARMACY</t>
+        </is>
+      </c>
+      <c r="C108" t="n">
+        <v>23498.06</v>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>DEMO-PESS-021</t>
+        </is>
+      </c>
+      <c r="E108" t="n">
+        <v>0</v>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>AOA</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>PAGO</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="2" t="n">
+        <v>45586</v>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>PHARMACY</t>
+        </is>
+      </c>
+      <c r="C109" t="n">
+        <v>16066.32</v>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>DEMO-PESS-026</t>
+        </is>
+      </c>
+      <c r="E109" t="n">
+        <v>0</v>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>AOA</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>PAGO</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="2" t="n">
+        <v>45586</v>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>OUTPATIENT</t>
+        </is>
+      </c>
+      <c r="C110" t="n">
+        <v>25547.76</v>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>DEMO-PESS-016</t>
+        </is>
+      </c>
+      <c r="E110" t="n">
+        <v>0</v>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>AOA</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>PAGO</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="2" t="n">
+        <v>45591</v>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>PHARMACY</t>
+        </is>
+      </c>
+      <c r="C111" t="n">
+        <v>20814.87</v>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>DEMO-PESS-010</t>
+        </is>
+      </c>
+      <c r="E111" t="n">
+        <v>0</v>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>AOA</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>REJEITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="2" t="n">
+        <v>45596</v>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>PHYSIOTHERAPY</t>
+        </is>
+      </c>
+      <c r="C112" t="n">
+        <v>34177.29</v>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>DEMO-PESS-027</t>
+        </is>
+      </c>
+      <c r="E112" t="n">
+        <v>0</v>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>AOA</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>PAGO</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="2" t="n">
+        <v>45603</v>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>OUTPATIENT</t>
+        </is>
+      </c>
+      <c r="C113" t="n">
+        <v>40043.78</v>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>DEMO-PESS-023</t>
+        </is>
+      </c>
+      <c r="E113" t="n">
+        <v>0</v>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>AOA</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>PAGO</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="2" t="n">
+        <v>45608</v>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>OUTPATIENT</t>
+        </is>
+      </c>
+      <c r="C114" t="n">
+        <v>30041.91</v>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>DEMO-PESS-009</t>
+        </is>
+      </c>
+      <c r="E114" t="n">
+        <v>0</v>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>AOA</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>PAGO</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="2" t="n">
+        <v>45615</v>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>EMERGENCY</t>
+        </is>
+      </c>
+      <c r="C115" t="n">
+        <v>27901.8</v>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>DEMO-PESS-013</t>
+        </is>
+      </c>
+      <c r="E115" t="n">
+        <v>0</v>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>AOA</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>PAGO</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="2" t="n">
+        <v>45620</v>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>OUTPATIENT</t>
+        </is>
+      </c>
+      <c r="C116" t="n">
+        <v>15324.8</v>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>DEMO-PESS-029</t>
+        </is>
+      </c>
+      <c r="E116" t="n">
+        <v>0</v>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>AOA</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>PAGO</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="n">
+        <v>45636</v>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>OUTPATIENT</t>
+        </is>
+      </c>
+      <c r="C117" t="n">
+        <v>21744.63</v>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>DEMO-PESS-010</t>
+        </is>
+      </c>
+      <c r="E117" t="n">
+        <v>0</v>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>AOA</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>PAGO</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="n">
+        <v>45637</v>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>ENDEMIC_DISEASES</t>
+        </is>
+      </c>
+      <c r="C118" t="n">
+        <v>31424.71</v>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>DEMO-PESS-010</t>
+        </is>
+      </c>
+      <c r="E118" t="n">
+        <v>0</v>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>AOA</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>PAGO</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="n">
+        <v>45639</v>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>PHARMACY</t>
+        </is>
+      </c>
+      <c r="C119" t="n">
+        <v>10151.34</v>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>DEMO-PESS-024</t>
+        </is>
+      </c>
+      <c r="E119" t="n">
+        <v>0</v>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>AOA</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>PAGO</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="n">
+        <v>45643</v>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>PHARMACY</t>
+        </is>
+      </c>
+      <c r="C120" t="n">
+        <v>23865.03</v>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>DEMO-PESS-022</t>
+        </is>
+      </c>
+      <c r="E120" t="n">
+        <v>0</v>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>AOA</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>PAGO</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="n">
+        <v>45643</v>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>OUTPATIENT</t>
+        </is>
+      </c>
+      <c r="C121" t="n">
+        <v>15462.41</v>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>DEMO-PESS-005</t>
+        </is>
+      </c>
+      <c r="E121" t="n">
+        <v>0</v>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>AOA</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>PAGO</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="n">
+        <v>45645</v>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>OUTPATIENT</t>
+        </is>
+      </c>
+      <c r="C122" t="n">
+        <v>33854.75</v>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>DEMO-PESS-007</t>
+        </is>
+      </c>
+      <c r="E122" t="n">
+        <v>0</v>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>AOA</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>PAGO</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="n">
+        <v>45663</v>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>VACCINATION</t>
+        </is>
+      </c>
+      <c r="C123" t="n">
+        <v>12219.8</v>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>DEMO-PESS-003</t>
+        </is>
+      </c>
+      <c r="E123" t="n">
+        <v>0</v>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>AOA</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>PAGO</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="n">
+        <v>45678</v>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>OPTICAL</t>
+        </is>
+      </c>
+      <c r="C124" t="n">
+        <v>41800.42</v>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>DEMO-PESS-014</t>
+        </is>
+      </c>
+      <c r="E124" t="n">
+        <v>0</v>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>AOA</t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>PAGO</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="n">
+        <v>45682</v>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>PHARMACY</t>
+        </is>
+      </c>
+      <c r="C125" t="n">
+        <v>25846.8</v>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>DEMO-PESS-029</t>
+        </is>
+      </c>
+      <c r="E125" t="n">
+        <v>0</v>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>AOA</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>PAGO</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="n">
+        <v>45693</v>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>PHARMACY</t>
+        </is>
+      </c>
+      <c r="C126" t="n">
+        <v>9606.639999999999</v>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>DEMO-PESS-029</t>
+        </is>
+      </c>
+      <c r="E126" t="n">
+        <v>0</v>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>AOA</t>
+        </is>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>PAGO</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="n">
+        <v>45706</v>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>OUTPATIENT</t>
+        </is>
+      </c>
+      <c r="C127" t="n">
+        <v>17089.46</v>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>DEMO-PESS-020</t>
+        </is>
+      </c>
+      <c r="E127" t="n">
+        <v>0</v>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>AOA</t>
+        </is>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>PAGO</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="n">
+        <v>45710</v>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>OUTPATIENT</t>
+        </is>
+      </c>
+      <c r="C128" t="n">
+        <v>41116.7</v>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>DEMO-PESS-021</t>
+        </is>
+      </c>
+      <c r="E128" t="n">
+        <v>0</v>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>AOA</t>
+        </is>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>PAGO</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="n">
+        <v>45715</v>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>ENDEMIC_DISEASES</t>
+        </is>
+      </c>
+      <c r="C129" t="n">
+        <v>26236.72</v>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>DEMO-PESS-012</t>
+        </is>
+      </c>
+      <c r="E129" t="n">
+        <v>0</v>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>AOA</t>
+        </is>
+      </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>PAGO</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="n">
+        <v>45719</v>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>DENTAL</t>
+        </is>
+      </c>
+      <c r="C130" t="n">
+        <v>35965.92</v>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>DEMO-PESS-020</t>
+        </is>
+      </c>
+      <c r="E130" t="n">
+        <v>0</v>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>AOA</t>
+        </is>
+      </c>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>PAGO</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="2" t="n">
+        <v>45720</v>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>OUTPATIENT</t>
+        </is>
+      </c>
+      <c r="C131" t="n">
+        <v>23477.37</v>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>DEMO-PESS-030</t>
+        </is>
+      </c>
+      <c r="E131" t="n">
+        <v>0</v>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>AOA</t>
+        </is>
+      </c>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>PAGO</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="n">
+        <v>45727</v>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>OUTPATIENT</t>
+        </is>
+      </c>
+      <c r="C132" t="n">
+        <v>27990.64</v>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>DEMO-PESS-028</t>
+        </is>
+      </c>
+      <c r="E132" t="n">
+        <v>0</v>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>AOA</t>
+        </is>
+      </c>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>REJEITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="2" t="n">
+        <v>45734</v>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>PHARMACY</t>
+        </is>
+      </c>
+      <c r="C133" t="n">
+        <v>17416.82</v>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>DEMO-PESS-027</t>
+        </is>
+      </c>
+      <c r="E133" t="n">
+        <v>0</v>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>AOA</t>
+        </is>
+      </c>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>PAGO</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="2" t="n">
+        <v>45757</v>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>PHARMACY</t>
+        </is>
+      </c>
+      <c r="C134" t="n">
+        <v>11836.69</v>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>DEMO-PESS-022</t>
+        </is>
+      </c>
+      <c r="E134" t="n">
+        <v>0</v>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>AOA</t>
+        </is>
+      </c>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>PAGO</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="2" t="n">
+        <v>45758</v>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>OUTPATIENT</t>
+        </is>
+      </c>
+      <c r="C135" t="n">
+        <v>26275.69</v>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>DEMO-PESS-018</t>
+        </is>
+      </c>
+      <c r="E135" t="n">
+        <v>0</v>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>AOA</t>
+        </is>
+      </c>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>PAGO</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="2" t="n">
+        <v>45762</v>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>HOSPITALIZATION</t>
+        </is>
+      </c>
+      <c r="C136" t="n">
+        <v>608844.13</v>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>DEMO-PESS-012</t>
+        </is>
+      </c>
+      <c r="E136" t="n">
+        <v>0</v>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>AOA</t>
+        </is>
+      </c>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>REJEITADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="2" t="n">
+        <v>45772</v>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>OUTPATIENT</t>
+        </is>
+      </c>
+      <c r="C137" t="n">
+        <v>44189.99</v>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>DEMO-PESS-026</t>
+        </is>
+      </c>
+      <c r="E137" t="n">
+        <v>0</v>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>AOA</t>
+        </is>
+      </c>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>PAGO</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="2" t="n">
+        <v>45777</v>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>PHARMACY</t>
+        </is>
+      </c>
+      <c r="C138" t="n">
+        <v>25758.43</v>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>DEMO-PESS-022</t>
+        </is>
+      </c>
+      <c r="E138" t="n">
+        <v>0</v>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>AOA</t>
+        </is>
+      </c>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>PAGO</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="2" t="n">
+        <v>45782</v>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>PHARMACY</t>
+        </is>
+      </c>
+      <c r="C139" t="n">
+        <v>15716.78</v>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>DEMO-PESS-019</t>
+        </is>
+      </c>
+      <c r="E139" t="n">
+        <v>0</v>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>AOA</t>
+        </is>
+      </c>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t>PAGO</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="2" t="n">
+        <v>45782</v>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>HOSPITALIZATION</t>
+        </is>
+      </c>
+      <c r="C140" t="n">
+        <v>365647.8</v>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>DEMO-PESS-011</t>
+        </is>
+      </c>
+      <c r="E140" t="n">
+        <v>0</v>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>AOA</t>
+        </is>
+      </c>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>PAGO</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="2" t="n">
+        <v>45783</v>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>PHARMACY</t>
+        </is>
+      </c>
+      <c r="C141" t="n">
+        <v>10322.69</v>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>DEMO-PESS-015</t>
+        </is>
+      </c>
+      <c r="E141" t="n">
+        <v>0</v>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>AOA</t>
+        </is>
+      </c>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>PAGO</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="2" t="n">
+        <v>45788</v>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>DENTAL</t>
+        </is>
+      </c>
+      <c r="C142" t="n">
+        <v>29655.07</v>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>DEMO-PESS-028</t>
+        </is>
+      </c>
+      <c r="E142" t="n">
+        <v>0</v>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>AOA</t>
+        </is>
+      </c>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>PAGO</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="2" t="n">
+        <v>45791</v>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>DENTAL</t>
+        </is>
+      </c>
+      <c r="C143" t="n">
+        <v>60739.17</v>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>DEMO-PESS-019</t>
+        </is>
+      </c>
+      <c r="E143" t="n">
+        <v>0</v>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>AOA</t>
+        </is>
+      </c>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>PAGO</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="2" t="n">
+        <v>45800</v>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>OUTPATIENT</t>
+        </is>
+      </c>
+      <c r="C144" t="n">
+        <v>42351.46</v>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>DEMO-PESS-025</t>
+        </is>
+      </c>
+      <c r="E144" t="n">
+        <v>0</v>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>AOA</t>
+        </is>
+      </c>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>PAGO</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="2" t="n">
+        <v>45812</v>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>PHARMACY</t>
+        </is>
+      </c>
+      <c r="C145" t="n">
+        <v>20941.85</v>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>DEMO-PESS-030</t>
+        </is>
+      </c>
+      <c r="E145" t="n">
+        <v>0</v>
+      </c>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>AOA</t>
+        </is>
+      </c>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>PAGO</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="2" t="n">
+        <v>45813</v>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>PHARMACY</t>
+        </is>
+      </c>
+      <c r="C146" t="n">
+        <v>18348.6</v>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>DEMO-PESS-004</t>
+        </is>
+      </c>
+      <c r="E146" t="n">
+        <v>0</v>
+      </c>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>AOA</t>
+        </is>
+      </c>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>PAGO</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="2" t="n">
+        <v>45826</v>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>OUTPATIENT</t>
+        </is>
+      </c>
+      <c r="C147" t="n">
+        <v>32686.93</v>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>DEMO-PESS-008</t>
+        </is>
+      </c>
+      <c r="E147" t="n">
+        <v>0</v>
+      </c>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>AOA</t>
+        </is>
+      </c>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>PAGO</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="2" t="n">
+        <v>45826</v>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>PHARMACY</t>
+        </is>
+      </c>
+      <c r="C148" t="n">
+        <v>21762.17</v>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>DEMO-PESS-022</t>
+        </is>
+      </c>
+      <c r="E148" t="n">
+        <v>0</v>
+      </c>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>AOA</t>
+        </is>
+      </c>
+      <c r="G148" t="inlineStr">
+        <is>
+          <t>PAGO</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="2" t="n">
+        <v>45827</v>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>OUTPATIENT</t>
+        </is>
+      </c>
+      <c r="C149" t="n">
+        <v>27116.11</v>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>DEMO-PESS-013</t>
+        </is>
+      </c>
+      <c r="E149" t="n">
+        <v>0</v>
+      </c>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>AOA</t>
+        </is>
+      </c>
+      <c r="G149" t="inlineStr">
+        <is>
+          <t>PAGO</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="2" t="n">
+        <v>45830</v>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>PHARMACY</t>
+        </is>
+      </c>
+      <c r="C150" t="n">
+        <v>24641.84</v>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>DEMO-PESS-027</t>
+        </is>
+      </c>
+      <c r="E150" t="n">
+        <v>0</v>
+      </c>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>AOA</t>
+        </is>
+      </c>
+      <c r="G150" t="inlineStr">
+        <is>
+          <t>PAGO</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="2" t="n">
+        <v>45843</v>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>ENDEMIC_DISEASES</t>
+        </is>
+      </c>
+      <c r="C151" t="n">
+        <v>25020.41</v>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>DEMO-PESS-021</t>
+        </is>
+      </c>
+      <c r="E151" t="n">
+        <v>0</v>
+      </c>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t>AOA</t>
+        </is>
+      </c>
+      <c r="G151" t="inlineStr">
+        <is>
+          <t>PAGO</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="2" t="n">
+        <v>45844</v>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>PHARMACY</t>
+        </is>
+      </c>
+      <c r="C152" t="n">
+        <v>6231.34</v>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>DEMO-PESS-018</t>
+        </is>
+      </c>
+      <c r="E152" t="n">
+        <v>0</v>
+      </c>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>AOA</t>
+        </is>
+      </c>
+      <c r="G152" t="inlineStr">
+        <is>
+          <t>PAGO</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="2" t="n">
+        <v>45859</v>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>PHARMACY</t>
+        </is>
+      </c>
+      <c r="C153" t="n">
+        <v>13269.8</v>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>DEMO-PESS-030</t>
+        </is>
+      </c>
+      <c r="E153" t="n">
+        <v>0</v>
+      </c>
+      <c r="F153" t="inlineStr">
+        <is>
+          <t>AOA</t>
+        </is>
+      </c>
+      <c r="G153" t="inlineStr">
+        <is>
+          <t>PAGO</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="2" t="n">
+        <v>45865</v>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>EMERGENCY</t>
+        </is>
+      </c>
+      <c r="C154" t="n">
+        <v>75583.08</v>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>DEMO-PESS-016</t>
+        </is>
+      </c>
+      <c r="E154" t="n">
+        <v>0</v>
+      </c>
+      <c r="F154" t="inlineStr">
+        <is>
+          <t>AOA</t>
+        </is>
+      </c>
+      <c r="G154" t="inlineStr">
+        <is>
+          <t>PAGO</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="2" t="n">
+        <v>45871</v>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>PHARMACY</t>
+        </is>
+      </c>
+      <c r="C155" t="n">
+        <v>22659.94</v>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>DEMO-PESS-021</t>
+        </is>
+      </c>
+      <c r="E155" t="n">
+        <v>0</v>
+      </c>
+      <c r="F155" t="inlineStr">
+        <is>
+          <t>AOA</t>
+        </is>
+      </c>
+      <c r="G155" t="inlineStr">
+        <is>
+          <t>PAGO</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="2" t="n">
+        <v>45876</v>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>OUTPATIENT</t>
+        </is>
+      </c>
+      <c r="C156" t="n">
+        <v>38094.58</v>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>DEMO-PESS-017</t>
+        </is>
+      </c>
+      <c r="E156" t="n">
+        <v>0</v>
+      </c>
+      <c r="F156" t="inlineStr">
+        <is>
+          <t>AOA</t>
+        </is>
+      </c>
+      <c r="G156" t="inlineStr">
+        <is>
+          <t>PAGO</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" s="2" t="n">
+        <v>45877</v>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>OUTPATIENT</t>
+        </is>
+      </c>
+      <c r="C157" t="n">
+        <v>43121.94</v>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>DEMO-PESS-007</t>
+        </is>
+      </c>
+      <c r="E157" t="n">
+        <v>0</v>
+      </c>
+      <c r="F157" t="inlineStr">
+        <is>
+          <t>AOA</t>
+        </is>
+      </c>
+      <c r="G157" t="inlineStr">
+        <is>
+          <t>PAGO</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" s="2" t="n">
+        <v>45887</v>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>HOSPITALIZATION</t>
+        </is>
+      </c>
+      <c r="C158" t="n">
+        <v>534469.41</v>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>DEMO-PESS-004</t>
+        </is>
+      </c>
+      <c r="E158" t="n">
+        <v>0</v>
+      </c>
+      <c r="F158" t="inlineStr">
+        <is>
+          <t>AOA</t>
+        </is>
+      </c>
+      <c r="G158" t="inlineStr">
+        <is>
+          <t>PAGO</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" s="2" t="n">
+        <v>45890</v>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>OUTPATIENT</t>
+        </is>
+      </c>
+      <c r="C159" t="n">
+        <v>24191.33</v>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>DEMO-PESS-018</t>
+        </is>
+      </c>
+      <c r="E159" t="n">
+        <v>0</v>
+      </c>
+      <c r="F159" t="inlineStr">
+        <is>
+          <t>AOA</t>
+        </is>
+      </c>
+      <c r="G159" t="inlineStr">
+        <is>
+          <t>PAGO</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" s="2" t="n">
+        <v>45897</v>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>OUTPATIENT</t>
+        </is>
+      </c>
+      <c r="C160" t="n">
+        <v>43085.93</v>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>DEMO-PESS-011</t>
+        </is>
+      </c>
+      <c r="E160" t="n">
+        <v>0</v>
+      </c>
+      <c r="F160" t="inlineStr">
+        <is>
+          <t>AOA</t>
+        </is>
+      </c>
+      <c r="G160" t="inlineStr">
+        <is>
+          <t>PAGO</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" s="2" t="n">
+        <v>45903</v>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>ENDEMIC_DISEASES</t>
+        </is>
+      </c>
+      <c r="C161" t="n">
+        <v>32028.77</v>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>DEMO-PESS-023</t>
+        </is>
+      </c>
+      <c r="E161" t="n">
+        <v>0</v>
+      </c>
+      <c r="F161" t="inlineStr">
+        <is>
+          <t>AOA</t>
+        </is>
+      </c>
+      <c r="G161" t="inlineStr">
+        <is>
+          <t>PAGO</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" s="2" t="n">
+        <v>45908</v>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>ENDEMIC_DISEASES</t>
+        </is>
+      </c>
+      <c r="C162" t="n">
+        <v>44651.97</v>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>DEMO-PESS-030</t>
+        </is>
+      </c>
+      <c r="E162" t="n">
+        <v>0</v>
+      </c>
+      <c r="F162" t="inlineStr">
+        <is>
+          <t>AOA</t>
+        </is>
+      </c>
+      <c r="G162" t="inlineStr">
+        <is>
+          <t>PAGO</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" s="2" t="n">
+        <v>45914</v>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>OUTPATIENT</t>
+        </is>
+      </c>
+      <c r="C163" t="n">
+        <v>13467.81</v>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>DEMO-PESS-018</t>
+        </is>
+      </c>
+      <c r="E163" t="n">
+        <v>0</v>
+      </c>
+      <c r="F163" t="inlineStr">
+        <is>
+          <t>AOA</t>
+        </is>
+      </c>
+      <c r="G163" t="inlineStr">
+        <is>
+          <t>PAGO</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" s="2" t="n">
+        <v>45919</v>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>PHARMACY</t>
+        </is>
+      </c>
+      <c r="C164" t="n">
+        <v>18301.46</v>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>DEMO-PESS-004</t>
+        </is>
+      </c>
+      <c r="E164" t="n">
+        <v>0</v>
+      </c>
+      <c r="F164" t="inlineStr">
+        <is>
+          <t>AOA</t>
+        </is>
+      </c>
+      <c r="G164" t="inlineStr">
+        <is>
+          <t>PAGO</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" s="2" t="n">
+        <v>45932</v>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>OPTICAL</t>
+        </is>
+      </c>
+      <c r="C165" t="n">
+        <v>47525.91</v>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>DEMO-PESS-005</t>
+        </is>
+      </c>
+      <c r="E165" t="n">
+        <v>0</v>
+      </c>
+      <c r="F165" t="inlineStr">
+        <is>
+          <t>AOA</t>
+        </is>
+      </c>
+      <c r="G165" t="inlineStr">
+        <is>
+          <t>PAGO</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" s="2" t="n">
+        <v>45937</v>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>ENDEMIC_DISEASES</t>
+        </is>
+      </c>
+      <c r="C166" t="n">
+        <v>26026.25</v>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>DEMO-PESS-017</t>
+        </is>
+      </c>
+      <c r="E166" t="n">
+        <v>0</v>
+      </c>
+      <c r="F166" t="inlineStr">
+        <is>
+          <t>AOA</t>
+        </is>
+      </c>
+      <c r="G166" t="inlineStr">
+        <is>
+          <t>PAGO</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" s="2" t="n">
+        <v>45939</v>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>EMERGENCY</t>
+        </is>
+      </c>
+      <c r="C167" t="n">
+        <v>56740.55</v>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>DEMO-PESS-011</t>
+        </is>
+      </c>
+      <c r="E167" t="n">
+        <v>0</v>
+      </c>
+      <c r="F167" t="inlineStr">
+        <is>
+          <t>AOA</t>
+        </is>
+      </c>
+      <c r="G167" t="inlineStr">
+        <is>
+          <t>PAGO</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" s="2" t="n">
+        <v>45941</v>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>HOSPITALIZATION</t>
+        </is>
+      </c>
+      <c r="C168" t="n">
+        <v>321779.06</v>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>DEMO-PESS-011</t>
+        </is>
+      </c>
+      <c r="E168" t="n">
+        <v>0</v>
+      </c>
+      <c r="F168" t="inlineStr">
+        <is>
+          <t>AOA</t>
+        </is>
+      </c>
+      <c r="G168" t="inlineStr">
+        <is>
+          <t>PAGO</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" s="2" t="n">
+        <v>45943</v>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>OPTICAL</t>
+        </is>
+      </c>
+      <c r="C169" t="n">
+        <v>35642.37</v>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>DEMO-PESS-019</t>
+        </is>
+      </c>
+      <c r="E169" t="n">
+        <v>0</v>
+      </c>
+      <c r="F169" t="inlineStr">
+        <is>
+          <t>AOA</t>
+        </is>
+      </c>
+      <c r="G169" t="inlineStr">
+        <is>
+          <t>PAGO</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" s="2" t="n">
+        <v>45956</v>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>OUTPATIENT</t>
+        </is>
+      </c>
+      <c r="C170" t="n">
+        <v>24084.19</v>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>DEMO-PESS-027</t>
+        </is>
+      </c>
+      <c r="E170" t="n">
+        <v>0</v>
+      </c>
+      <c r="F170" t="inlineStr">
+        <is>
+          <t>AOA</t>
+        </is>
+      </c>
+      <c r="G170" t="inlineStr">
+        <is>
+          <t>PAGO</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" s="2" t="n">
+        <v>45977</v>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>OPTICAL</t>
+        </is>
+      </c>
+      <c r="C171" t="n">
+        <v>0</v>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>DEMO-PESS-028</t>
+        </is>
+      </c>
+      <c r="E171" t="n">
+        <v>46574.35</v>
+      </c>
+      <c r="F171" t="inlineStr">
+        <is>
+          <t>AOA</t>
+        </is>
+      </c>
+      <c r="G171" t="inlineStr">
+        <is>
+          <t>ABERTO</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" s="2" t="n">
+        <v>45978</v>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>EMERGENCY</t>
+        </is>
+      </c>
+      <c r="C172" t="n">
+        <v>0</v>
+      </c>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>DEMO-PESS-025</t>
+        </is>
+      </c>
+      <c r="E172" t="n">
+        <v>69333.67</v>
+      </c>
+      <c r="F172" t="inlineStr">
+        <is>
+          <t>AOA</t>
+        </is>
+      </c>
+      <c r="G172" t="inlineStr">
+        <is>
+          <t>ABERTO</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" s="2" t="n">
+        <v>45989</v>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>DENTAL</t>
+        </is>
+      </c>
+      <c r="C173" t="n">
+        <v>0</v>
+      </c>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>DEMO-PESS-024</t>
+        </is>
+      </c>
+      <c r="E173" t="n">
+        <v>18550.49</v>
+      </c>
+      <c r="F173" t="inlineStr">
+        <is>
+          <t>AOA</t>
+        </is>
+      </c>
+      <c r="G173" t="inlineStr">
+        <is>
+          <t>ABERTO</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" s="2" t="n">
+        <v>45998</v>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>CHECKUP_PREVENTIVE</t>
+        </is>
+      </c>
+      <c r="C174" t="n">
+        <v>0</v>
+      </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>DEMO-PESS-008</t>
+        </is>
+      </c>
+      <c r="E174" t="n">
+        <v>18490.89</v>
+      </c>
+      <c r="F174" t="inlineStr">
+        <is>
+          <t>AOA</t>
+        </is>
+      </c>
+      <c r="G174" t="inlineStr">
+        <is>
+          <t>ABERTO</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" s="2" t="n">
+        <v>46009</v>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>OUTPATIENT</t>
+        </is>
+      </c>
+      <c r="C175" t="n">
+        <v>0</v>
+      </c>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>DEMO-PESS-006</t>
+        </is>
+      </c>
+      <c r="E175" t="n">
+        <v>40495.48</v>
+      </c>
+      <c r="F175" t="inlineStr">
+        <is>
+          <t>AOA</t>
+        </is>
+      </c>
+      <c r="G175" t="inlineStr">
+        <is>
+          <t>ABERTO</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" s="2" t="n">
+        <v>46013</v>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>PHARMACY</t>
+        </is>
+      </c>
+      <c r="C176" t="n">
+        <v>0</v>
+      </c>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>DEMO-PESS-006</t>
+        </is>
+      </c>
+      <c r="E176" t="n">
+        <v>13471.4</v>
+      </c>
+      <c r="F176" t="inlineStr">
+        <is>
+          <t>AOA</t>
+        </is>
+      </c>
+      <c r="G176" t="inlineStr">
+        <is>
+          <t>ABERTO</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" s="2" t="n">
+        <v>46019</v>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>PHARMACY</t>
+        </is>
+      </c>
+      <c r="C177" t="n">
+        <v>0</v>
+      </c>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>DEMO-PESS-004</t>
+        </is>
+      </c>
+      <c r="E177" t="n">
+        <v>14422.23</v>
+      </c>
+      <c r="F177" t="inlineStr">
+        <is>
+          <t>AOA</t>
+        </is>
+      </c>
+      <c r="G177" t="inlineStr">
+        <is>
+          <t>ABERTO</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" s="2" t="n">
+        <v>46022</v>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>ENDEMIC_DISEASES</t>
+        </is>
+      </c>
+      <c r="C178" t="n">
+        <v>0</v>
+      </c>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>DEMO-PESS-028</t>
+        </is>
+      </c>
+      <c r="E178" t="n">
+        <v>43424.18</v>
+      </c>
+      <c r="F178" t="inlineStr">
+        <is>
+          <t>AOA</t>
+        </is>
+      </c>
+      <c r="G178" t="inlineStr">
+        <is>
+          <t>ABERTO</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G37"/>
+  <autoFilter ref="A1:G178"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1612,7 +5984,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B7"/>
+  <dimension ref="A1:B8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1639,7 +6011,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>Histórico fictício de 36 meses para ensaiar importação e indicadores.</t>
+          <t>Histórico fictício de 36 meses (177 sinistros) para ensaiar importação e indicadores.</t>
         </is>
       </c>
     </row>
@@ -1700,6 +6072,18 @@
       <c r="B7" s="3" t="inlineStr">
         <is>
           <t>Use o modelo vazio com dados da seguradora.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Estados</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Inclui sinistros pagos, rejeitados, em aberto com provisão e um em USD.</t>
         </is>
       </c>
     </row>
